--- a/英文问答表.xlsx
+++ b/英文问答表.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
-  <workbookPr/>
+  <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
     <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="28">
   <si>
     <t>问题</t>
   </si>
@@ -76,6 +76,20 @@
 Could you please arrange to have the package (tracking number: XXX) delivered to a self-pickup point? This would be much more convenient for recipient.
 Thanks for your help!
 Best,</t>
+  </si>
+  <si>
+    <t>催派</t>
+  </si>
+  <si>
+    <t>【标题】Expedite Parcel Delivery
+【正文】
+Dear CTT Team,
+This is Bella from AWESUNG Inc.
+We urgently request you to expedite the delivery of the following parcel:
+Tracking# 
+Please prioritize this shipment and update us on the delivery progress promptly.
+Thank you.
+Best regards,</t>
   </si>
   <si>
     <t>申请重派</t>
@@ -145,6 +159,16 @@
     <t>Dear XXX Team,
 Could you please advise if there is any update available?
 Thanks for your assistance.
+Best regards,</t>
+  </si>
+  <si>
+    <t>催回复（加强版）</t>
+  </si>
+  <si>
+    <t>Hi Team,
+We’re reaching out again to follow up on our previous request.
+We haven’t received any update yet and would appreciate it if you could provide the latest status at your earliest convenience. This will help us proceed with our subsequent work smoothly.
+Thank you for your attention to this matter.
 Best regards,</t>
   </si>
   <si>
@@ -1097,7 +1121,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C12"/>
+  <dimension ref="A1:C14"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="2" width="25.375" customWidth="1"/>
@@ -1159,15 +1183,15 @@
         <v>13</v>
       </c>
       <c r="B7" t="s">
-        <v>6</v>
+        <v>14</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B8" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -1200,6 +1224,22 @@
       </c>
       <c r="B12" t="s">
         <v>23</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13" t="s">
+        <v>24</v>
+      </c>
+      <c r="B13" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14" t="s">
+        <v>26</v>
+      </c>
+      <c r="B14" t="s">
+        <v>27</v>
       </c>
     </row>
   </sheetData>
